--- a/src/core/档案模版.xlsx
+++ b/src/core/档案模版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28695" windowHeight="14070" activeTab="1"/>
+    <workbookView windowWidth="28695" windowHeight="14070" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="文书档案-案卷级" sheetId="1" r:id="rId1"/>
@@ -15,13 +15,14 @@
     <sheet name="会计档案-文件级" sheetId="6" r:id="rId6"/>
     <sheet name="科技档案-案卷级" sheetId="7" r:id="rId7"/>
     <sheet name="科技档案-文件级" sheetId="8" r:id="rId8"/>
+    <sheet name="合同档案-案卷级" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113">
   <si>
     <t>序号</t>
   </si>
@@ -243,6 +244,123 @@
   </si>
   <si>
     <t>检查日期</t>
+  </si>
+  <si>
+    <t>合同名称</t>
+  </si>
+  <si>
+    <t>年度</t>
+  </si>
+  <si>
+    <t>gdnd</t>
+  </si>
+  <si>
+    <t>合同责任人（项目责任人）</t>
+  </si>
+  <si>
+    <t>登记日期</t>
+  </si>
+  <si>
+    <t>合同类别</t>
+  </si>
+  <si>
+    <t>htlb</t>
+  </si>
+  <si>
+    <t>合同编号</t>
+  </si>
+  <si>
+    <t>bh</t>
+  </si>
+  <si>
+    <t>主要内容</t>
+  </si>
+  <si>
+    <t>zynr</t>
+  </si>
+  <si>
+    <t>签订日期</t>
+  </si>
+  <si>
+    <t>qdrq</t>
+  </si>
+  <si>
+    <t>项目截止日期</t>
+  </si>
+  <si>
+    <t>xmjzrq</t>
+  </si>
+  <si>
+    <t>对方单位</t>
+  </si>
+  <si>
+    <t>dfdw</t>
+  </si>
+  <si>
+    <t>对方联系人</t>
+  </si>
+  <si>
+    <t>dflxr</t>
+  </si>
+  <si>
+    <t>对方联系方式</t>
+  </si>
+  <si>
+    <t>dflxfs</t>
+  </si>
+  <si>
+    <t>合同金额</t>
+  </si>
+  <si>
+    <t>htje</t>
+  </si>
+  <si>
+    <t>支付方式</t>
+  </si>
+  <si>
+    <t>zffs</t>
+  </si>
+  <si>
+    <t>剩余金额</t>
+  </si>
+  <si>
+    <t>syje</t>
+  </si>
+  <si>
+    <t>履约状态</t>
+  </si>
+  <si>
+    <t>lyzt</t>
+  </si>
+  <si>
+    <t>商务对接人</t>
+  </si>
+  <si>
+    <t>swdjr</t>
+  </si>
+  <si>
+    <t>经办人</t>
+  </si>
+  <si>
+    <t>jbr</t>
+  </si>
+  <si>
+    <t>登记人</t>
+  </si>
+  <si>
+    <t>djr</t>
+  </si>
+  <si>
+    <t>最终客户</t>
+  </si>
+  <si>
+    <t>zzkh</t>
+  </si>
+  <si>
+    <t>合同执行期限</t>
+  </si>
+  <si>
+    <t>htzxqx</t>
   </si>
 </sst>
 </file>
@@ -250,18 +368,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="0"/>
     </font>
     <font>
       <b/>
@@ -279,6 +403,52 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
@@ -293,8 +463,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,7 +480,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -331,53 +510,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -393,23 +532,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -432,7 +556,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,49 +724,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -498,121 +736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -642,39 +766,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -691,11 +782,35 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -738,6 +853,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -746,10 +870,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -758,150 +882,156 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1605,246 +1735,246 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="12.8833333333333" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.8833333333333" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="4">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1">
         <v>30</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="4">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="4">
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1">
         <v>1000</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1">
         <v>20</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1">
         <v>300</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1">
         <v>300</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1">
         <v>20</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="1">
         <v>10</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1">
         <v>20</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1">
         <v>200</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="4">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="D11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1">
         <v>10</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="4">
+      <c r="D12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1">
         <v>1000</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="1" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1861,202 +1991,202 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="4">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1">
         <v>30</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="4">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="4">
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1">
         <v>20</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1">
         <v>1000</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1">
         <v>20</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1">
         <v>20</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="1">
         <v>10</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1">
         <v>20</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1">
         <v>20</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1">
         <v>1000</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="1" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2073,202 +2203,202 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5">
         <v>30</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
         <v>20</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="2">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="D4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5">
         <v>1000</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5">
         <v>100</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="D6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5">
         <v>50</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="D7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="5">
         <v>20</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="D8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="5">
         <v>1000</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1">
         <v>20</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1">
         <v>30</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2285,222 +2415,222 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="4">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1">
         <v>30</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="4">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="4">
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1">
         <v>20</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1">
         <v>50</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1">
         <v>1000</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1">
         <v>20</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="1">
         <v>10</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1">
         <v>1000</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1">
         <v>30</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1">
         <v>30</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="4">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="D11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1">
         <v>30</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="1" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2517,202 +2647,202 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="4">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1">
         <v>30</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="4">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="4">
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1">
         <v>300</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1">
         <v>300</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1">
         <v>1000</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1">
         <v>20</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="1">
         <v>10</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1">
         <v>20</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1">
         <v>1000</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1">
         <v>30</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2729,262 +2859,262 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5">
         <v>30</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
         <v>20</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="2">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="D4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5">
         <v>1000</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5">
         <v>20</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="5">
         <v>10</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="D7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="5">
         <v>20</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="D8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="5">
         <v>1000</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1">
         <v>500</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1">
         <v>20</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="2">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="D11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1">
         <v>20</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="4">
+      <c r="D12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1">
         <v>20</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="2">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="D13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1">
         <v>20</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="1" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3001,215 +3131,690 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5">
         <v>30</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
         <v>20</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="2">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="D4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5">
         <v>1000</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5">
         <v>300</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="D6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5">
         <v>20</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="5">
         <v>10</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="D8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="5">
         <v>20</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="D9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="5">
         <v>200</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="D10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5">
         <v>1000</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="28.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2">
+        <v>300</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2">
+        <v>20</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4000</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2">
+        <v>20</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2">
+        <v>20</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2">
+        <v>200</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2">
+        <v>20</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2">
+        <v>100</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="2">
+        <v>100</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="2">
+        <v>200</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2">
+        <v>100</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2">
+        <v>20</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2">
+        <v>200</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2">
+        <v>200</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="2">
+        <v>200</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="2">
+        <v>200</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="2">
+        <v>100</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
+  <headerFooter/>
+</worksheet>
 </file>